--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,0,1,1</t>
   </si>
   <si>
-    <t>0.4367,0.4588,0.0685,0.1621</t>
-  </si>
-  <si>
-    <t>0.0123,0.0080,0.0038,0.9891</t>
-  </si>
-  <si>
-    <t>0.5434,0.1128,0.0479,0.3446</t>
-  </si>
-  <si>
-    <t>0.0193,0.0193,0.0061,0.9824</t>
-  </si>
-  <si>
-    <t>0.9730,0.0230,0.0030,0.0049</t>
-  </si>
-  <si>
-    <t>0.9713,0.0186,0.0031,0.0066</t>
-  </si>
-  <si>
-    <t>0.9747,0.0187,0.0041,0.0039</t>
-  </si>
-  <si>
-    <t>0.9731,0.0199,0.0035,0.0053</t>
-  </si>
-  <si>
-    <t>0.9778,0.0183,0.0025,0.0034</t>
-  </si>
-  <si>
-    <t>0.9350,0.0779,0.0073,0.0075</t>
-  </si>
-  <si>
-    <t>0.9753,0.0114,0.0018,0.0088</t>
-  </si>
-  <si>
-    <t>0.9752,0.0146,0.0011,0.0084</t>
-  </si>
-  <si>
-    <t>0.3509,0.4737,0.2368,0.1308</t>
-  </si>
-  <si>
-    <t>0.1130,0.0403,0.9200,0.0026</t>
-  </si>
-  <si>
-    <t>0.0872,0.0272,0.9406,0.0019</t>
-  </si>
-  <si>
-    <t>0.1551,0.0134,0.9150,0.0025</t>
-  </si>
-  <si>
-    <t>0.2720,0.0566,0.6304,0.0910</t>
-  </si>
-  <si>
-    <t>0.0404,0.9473,0.0298,0.0018</t>
-  </si>
-  <si>
-    <t>0.1268,0.8797,0.0577,0.0068</t>
-  </si>
-  <si>
-    <t>0.8018,0.1924,0.0389,0.0249</t>
-  </si>
-  <si>
-    <t>0.2610,0.7339,0.0766,0.0147</t>
-  </si>
-  <si>
-    <t>0.2311,0.6685,0.1501,0.0053</t>
-  </si>
-  <si>
-    <t>0.2088,0.0400,0.5029,0.2562</t>
-  </si>
-  <si>
-    <t>0.0459,0.0419,0.7719,0.2302</t>
-  </si>
-  <si>
-    <t>0.0089,0.0030,0.9820,0.0190</t>
-  </si>
-  <si>
-    <t>0.2341,0.0259,0.7508,0.0366</t>
-  </si>
-  <si>
-    <t>0.0847,0.0258,0.9159,0.0144</t>
-  </si>
-  <si>
-    <t>0.0971,0.0099,0.9184,0.0190</t>
-  </si>
-  <si>
-    <t>0.0044,0.0019,0.9884,0.0212</t>
-  </si>
-  <si>
-    <t>0.2657,0.7473,0.0610,0.0138</t>
-  </si>
-  <si>
-    <t>0.3864,0.4838,0.1937,0.0120</t>
-  </si>
-  <si>
-    <t>0.0011,0.0010,0.9972,0.0065</t>
-  </si>
-  <si>
-    <t>0.0212,0.3658,0.8924,0.0019</t>
-  </si>
-  <si>
-    <t>0.8640,0.0895,0.0458,0.0289</t>
-  </si>
-  <si>
-    <t>0.6285,0.0629,0.4354,0.0110</t>
-  </si>
-  <si>
-    <t>0.8413,0.1955,0.0232,0.0108</t>
-  </si>
-  <si>
-    <t>0.0956,0.5097,0.6065,0.0095</t>
-  </si>
-  <si>
-    <t>0.0018,0.0343,0.9843,0.0093</t>
-  </si>
-  <si>
-    <t>0.0019,0.0079,0.9018,0.2354</t>
-  </si>
-  <si>
-    <t>0.0065,0.0120,0.8472,0.3142</t>
-  </si>
-  <si>
-    <t>0.0106,0.0079,0.5726,0.6980</t>
-  </si>
-  <si>
-    <t>0.0023,0.0044,0.9036,0.2853</t>
-  </si>
-  <si>
-    <t>0.0064,0.2371,0.9564,0.0057</t>
-  </si>
-  <si>
-    <t>0.0081,0.0171,0.7024,0.5203</t>
-  </si>
-  <si>
-    <t>0.4208,0.2850,0.1055,0.3402</t>
-  </si>
-  <si>
-    <t>0.0269,0.9274,0.1411,0.0085</t>
-  </si>
-  <si>
-    <t>0.0089,0.8839,0.6036,0.0041</t>
-  </si>
-  <si>
-    <t>0.0061,0.9668,0.2431,0.0011</t>
-  </si>
-  <si>
-    <t>0.0007,0.0157,0.9809,0.0281</t>
-  </si>
-  <si>
-    <t>0.0004,0.0051,0.9967,0.0044</t>
-  </si>
-  <si>
-    <t>0.0169,0.0088,0.9766,0.0140</t>
-  </si>
-  <si>
-    <t>0.0264,0.0055,0.9227,0.0898</t>
-  </si>
-  <si>
-    <t>0.0128,0.0056,0.9608,0.0498</t>
-  </si>
-  <si>
-    <t>0.0051,0.0051,0.9915,0.0068</t>
-  </si>
-  <si>
-    <t>0.9472,0.0486,0.0078,0.0077</t>
-  </si>
-  <si>
-    <t>0.9162,0.0248,0.0284,0.0289</t>
-  </si>
-  <si>
-    <t>0.8987,0.0745,0.0470,0.0105</t>
-  </si>
-  <si>
-    <t>0.0070,0.0078,0.9668,0.0513</t>
-  </si>
-  <si>
-    <t>0.9668,0.0271,0.0063,0.0048</t>
-  </si>
-  <si>
-    <t>0.9724,0.0185,0.0031,0.0064</t>
-  </si>
-  <si>
-    <t>0.9326,0.0725,0.0094,0.0078</t>
-  </si>
-  <si>
-    <t>0.0016,0.0883,0.9872,0.0037</t>
-  </si>
-  <si>
-    <t>0.0036,0.0231,0.9714,0.0312</t>
-  </si>
-  <si>
-    <t>0.0017,0.0027,0.9524,0.1805</t>
-  </si>
-  <si>
-    <t>0.0006,0.1889,0.9935,0.0011</t>
-  </si>
-  <si>
-    <t>0.0014,0.0034,0.9923,0.0142</t>
-  </si>
-  <si>
-    <t>0.0371,0.8611,0.3241,0.0062</t>
-  </si>
-  <si>
-    <t>0.0026,0.9624,0.3764,0.0007</t>
-  </si>
-  <si>
-    <t>0.6979,0.0796,0.3183,0.0205</t>
-  </si>
-  <si>
-    <t>0.4726,0.3543,0.2613,0.0387</t>
-  </si>
-  <si>
-    <t>0.0040,0.0106,0.9929,0.0036</t>
-  </si>
-  <si>
-    <t>0.0033,0.5655,0.9472,0.0038</t>
-  </si>
-  <si>
-    <t>0.0036,0.1083,0.9863,0.0028</t>
-  </si>
-  <si>
-    <t>0.0019,0.2452,0.9797,0.0030</t>
-  </si>
-  <si>
-    <t>0.0013,0.5000,0.9795,0.0008</t>
-  </si>
-  <si>
-    <t>0.0449,0.0126,0.0235,0.9569</t>
-  </si>
-  <si>
-    <t>0.0166,0.0078,0.0017,0.9885</t>
-  </si>
-  <si>
-    <t>0.0058,0.0078,0.0013,0.9944</t>
-  </si>
-  <si>
-    <t>0.0180,0.0154,0.0064,0.9825</t>
-  </si>
-  <si>
-    <t>0.0178,0.0116,0.0138,0.9795</t>
-  </si>
-  <si>
-    <t>0.0112,0.0156,0.0039,0.9879</t>
-  </si>
-  <si>
-    <t>0.0009,0.1177,0.9950,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.0367,0.9911,0.0047</t>
-  </si>
-  <si>
-    <t>0.0046,0.0238,0.9822,0.0129</t>
-  </si>
-  <si>
-    <t>0.0033,0.0116,0.9881,0.0099</t>
-  </si>
-  <si>
-    <t>0.0025,0.1029,0.9906,0.0019</t>
-  </si>
-  <si>
-    <t>0.0036,0.1977,0.9699,0.0065</t>
-  </si>
-  <si>
-    <t>0.9756,0.0162,0.0024,0.0053</t>
-  </si>
-  <si>
-    <t>0.9604,0.0344,0.0045,0.0071</t>
-  </si>
-  <si>
-    <t>0.9115,0.0828,0.0295,0.0085</t>
-  </si>
-  <si>
-    <t>0.9681,0.0245,0.0055,0.0056</t>
-  </si>
-  <si>
-    <t>0.9767,0.0163,0.0025,0.0042</t>
-  </si>
-  <si>
-    <t>0.9728,0.0233,0.0047,0.0037</t>
-  </si>
-  <si>
-    <t>0.9513,0.0353,0.0096,0.0099</t>
-  </si>
-  <si>
-    <t>0.9677,0.0296,0.0058,0.0044</t>
-  </si>
-  <si>
-    <t>0.9751,0.0145,0.0016,0.0076</t>
-  </si>
-  <si>
-    <t>0.9594,0.0226,0.0038,0.0136</t>
-  </si>
-  <si>
-    <t>0.9765,0.0188,0.0019,0.0048</t>
-  </si>
-  <si>
-    <t>0.9800,0.0130,0.0018,0.0049</t>
-  </si>
-  <si>
-    <t>0.9703,0.0215,0.0038,0.0057</t>
-  </si>
-  <si>
-    <t>0.9805,0.0134,0.0018,0.0045</t>
-  </si>
-  <si>
-    <t>0.9699,0.0195,0.0021,0.0092</t>
-  </si>
-  <si>
-    <t>0.9680,0.0246,0.0029,0.0067</t>
-  </si>
-  <si>
-    <t>0.0010,0.0016,0.9765,0.0971</t>
-  </si>
-  <si>
-    <t>0.0173,0.0059,0.9732,0.0174</t>
-  </si>
-  <si>
-    <t>0.3855,0.1358,0.1919,0.4019</t>
-  </si>
-  <si>
-    <t>0.0149,0.0057,0.9857,0.0043</t>
-  </si>
-  <si>
-    <t>0.1168,0.8443,0.0969,0.0058</t>
-  </si>
-  <si>
-    <t>0.1587,0.8461,0.0403,0.0076</t>
-  </si>
-  <si>
-    <t>0.4324,0.6328,0.0455,0.0087</t>
-  </si>
-  <si>
-    <t>0.6649,0.3372,0.0923,0.0160</t>
-  </si>
-  <si>
-    <t>0.1470,0.8090,0.1076,0.0134</t>
-  </si>
-  <si>
-    <t>0.0717,0.8931,0.0827,0.0026</t>
-  </si>
-  <si>
-    <t>0.5791,0.4564,0.0864,0.0185</t>
-  </si>
-  <si>
-    <t>0.3551,0.2349,0.4732,0.0283</t>
-  </si>
-  <si>
-    <t>0.2023,0.0186,0.8571,0.0065</t>
-  </si>
-  <si>
-    <t>0.3476,0.4029,0.2966,0.0271</t>
-  </si>
-  <si>
-    <t>0.2640,0.0453,0.7289,0.0287</t>
-  </si>
-  <si>
-    <t>0.4145,0.1335,0.4735,0.0866</t>
-  </si>
-  <si>
-    <t>0.0205,0.9228,0.3178,0.0043</t>
-  </si>
-  <si>
-    <t>0.0117,0.9635,0.0773,0.0034</t>
-  </si>
-  <si>
-    <t>0.4165,0.3197,0.3394,0.0468</t>
-  </si>
-  <si>
-    <t>0.0008,0.8935,0.9182,0.0005</t>
-  </si>
-  <si>
-    <t>0.0700,0.8903,0.1135,0.0054</t>
-  </si>
-  <si>
-    <t>0.8074,0.1594,0.0948,0.0059</t>
-  </si>
-  <si>
-    <t>0.7759,0.1845,0.1086,0.0130</t>
-  </si>
-  <si>
-    <t>0.8678,0.1285,0.0288,0.0143</t>
-  </si>
-  <si>
-    <t>0.9294,0.0187,0.0098,0.0348</t>
-  </si>
-  <si>
-    <t>0.9477,0.0233,0.0070,0.0195</t>
-  </si>
-  <si>
-    <t>0.9297,0.0528,0.0155,0.0132</t>
-  </si>
-  <si>
-    <t>0.9682,0.0161,0.0017,0.0123</t>
-  </si>
-  <si>
-    <t>0.8469,0.0854,0.0999,0.0165</t>
-  </si>
-  <si>
-    <t>0.9173,0.0540,0.0244,0.0180</t>
-  </si>
-  <si>
-    <t>0.9704,0.0156,0.0048,0.0069</t>
-  </si>
-  <si>
-    <t>0.0018,0.1817,0.9836,0.0033</t>
-  </si>
-  <si>
-    <t>0.0026,0.0695,0.9929,0.0013</t>
-  </si>
-  <si>
-    <t>0.0036,0.0292,0.9867,0.0073</t>
-  </si>
-  <si>
-    <t>0.0377,0.0871,0.9255,0.0178</t>
-  </si>
-  <si>
-    <t>0.5192,0.2737,0.1207,0.1806</t>
-  </si>
-  <si>
-    <t>0.4056,0.0845,0.3151,0.2586</t>
-  </si>
-  <si>
-    <t>0.1300,0.0146,0.9110,0.0071</t>
-  </si>
-  <si>
-    <t>0.4297,0.1900,0.4523,0.0504</t>
-  </si>
-  <si>
-    <t>0.0546,0.0207,0.0065,0.9578</t>
-  </si>
-  <si>
-    <t>0.0014,0.0038,0.0014,0.9978</t>
-  </si>
-  <si>
-    <t>0.0046,0.0068,0.0032,0.9944</t>
-  </si>
-  <si>
-    <t>0.0040,0.0050,0.0024,0.9956</t>
-  </si>
-  <si>
-    <t>0.0022,0.0822,0.9834,0.0054</t>
-  </si>
-  <si>
-    <t>0.9564,0.0303,0.0110,0.0072</t>
-  </si>
-  <si>
-    <t>0.7334,0.2633,0.0606,0.0204</t>
-  </si>
-  <si>
-    <t>0.9516,0.0392,0.0067,0.0094</t>
-  </si>
-  <si>
-    <t>0.7962,0.2467,0.0194,0.0162</t>
-  </si>
-  <si>
-    <t>0.9085,0.0309,0.0341,0.0294</t>
-  </si>
-  <si>
-    <t>0.7713,0.0471,0.0664,0.1305</t>
-  </si>
-  <si>
-    <t>0.9189,0.0324,0.0112,0.0321</t>
-  </si>
-  <si>
-    <t>0.0043,0.0060,0.7254,0.5664</t>
-  </si>
-  <si>
-    <t>0.8485,0.0421,0.0524,0.0572</t>
-  </si>
-  <si>
-    <t>0.6252,0.1607,0.1486,0.2061</t>
-  </si>
-  <si>
-    <t>0.1085,0.8623,0.0744,0.0058</t>
-  </si>
-  <si>
-    <t>0.5730,0.3937,0.1073,0.0483</t>
-  </si>
-  <si>
-    <t>0.7939,0.1633,0.0673,0.0394</t>
-  </si>
-  <si>
-    <t>0.5938,0.1874,0.3007,0.0442</t>
-  </si>
-  <si>
-    <t>0.5512,0.1723,0.3713,0.0371</t>
-  </si>
-  <si>
-    <t>0.6143,0.1498,0.3253,0.0238</t>
-  </si>
-  <si>
-    <t>0.9581,0.0198,0.0036,0.0153</t>
-  </si>
-  <si>
-    <t>0.9591,0.0305,0.0038,0.0108</t>
-  </si>
-  <si>
-    <t>0.9551,0.0302,0.0044,0.0114</t>
-  </si>
-  <si>
-    <t>0.9417,0.0425,0.0125,0.0120</t>
-  </si>
-  <si>
-    <t>0.9380,0.0462,0.0070,0.0162</t>
-  </si>
-  <si>
-    <t>0.9694,0.0239,0.0042,0.0049</t>
-  </si>
-  <si>
-    <t>0.9662,0.0189,0.0054,0.0086</t>
-  </si>
-  <si>
-    <t>0.9621,0.0163,0.0036,0.0143</t>
-  </si>
-  <si>
-    <t>0.1744,0.8203,0.0513,0.0214</t>
-  </si>
-  <si>
-    <t>0.6550,0.4410,0.0326,0.0061</t>
-  </si>
-  <si>
-    <t>0.5754,0.5233,0.0364,0.0046</t>
-  </si>
-  <si>
-    <t>0.6607,0.0775,0.4485,0.0059</t>
-  </si>
-  <si>
-    <t>0.9375,0.0614,0.0123,0.0070</t>
-  </si>
-  <si>
-    <t>0.9128,0.0838,0.0212,0.0100</t>
-  </si>
-  <si>
-    <t>0.9274,0.0709,0.0131,0.0094</t>
-  </si>
-  <si>
-    <t>0.9287,0.0553,0.0163,0.0110</t>
-  </si>
-  <si>
-    <t>0.0038,0.0033,0.9932,0.0067</t>
-  </si>
-  <si>
-    <t>0.9377,0.0488,0.0119,0.0101</t>
-  </si>
-  <si>
-    <t>0.0020,0.0066,0.9916,0.0097</t>
-  </si>
-  <si>
-    <t>0.0014,0.0035,0.9909,0.0191</t>
-  </si>
-  <si>
-    <t>0.1481,0.0932,0.8039,0.0227</t>
-  </si>
-  <si>
-    <t>0.0008,0.0118,0.9867,0.0191</t>
-  </si>
-  <si>
-    <t>0.0177,0.0138,0.9679,0.0240</t>
-  </si>
-  <si>
-    <t>0.0015,0.0008,0.9982,0.0023</t>
-  </si>
-  <si>
-    <t>0.0447,0.0098,0.9639,0.0071</t>
-  </si>
-  <si>
-    <t>0.3080,0.1910,0.5745,0.0257</t>
-  </si>
-  <si>
-    <t>0.4259,0.0451,0.6998,0.0038</t>
-  </si>
-  <si>
-    <t>0.4221,0.2155,0.3736,0.1536</t>
-  </si>
-  <si>
-    <t>0.1731,0.3761,0.5750,0.0128</t>
-  </si>
-  <si>
-    <t>0.1261,0.1637,0.7986,0.0141</t>
-  </si>
-  <si>
-    <t>0.3257,0.4702,0.2523,0.0448</t>
-  </si>
-  <si>
-    <t>0.5952,0.1720,0.2772,0.0543</t>
-  </si>
-  <si>
-    <t>0.2722,0.0695,0.7643,0.0071</t>
-  </si>
-  <si>
-    <t>0.8983,0.1491,0.0132,0.0040</t>
-  </si>
-  <si>
-    <t>0.7669,0.3029,0.0153,0.0165</t>
-  </si>
-  <si>
-    <t>0.8626,0.1335,0.0456,0.0082</t>
-  </si>
-  <si>
-    <t>0.9753,0.0187,0.0019,0.0053</t>
-  </si>
-  <si>
-    <t>0.9381,0.0746,0.0118,0.0047</t>
-  </si>
-  <si>
-    <t>0.2651,0.4521,0.3499,0.0494</t>
-  </si>
-  <si>
-    <t>0.4231,0.0534,0.6065,0.0278</t>
-  </si>
-  <si>
-    <t>0.3469,0.2066,0.4043,0.1508</t>
-  </si>
-  <si>
-    <t>0.1360,0.0169,0.7504,0.1067</t>
-  </si>
-  <si>
-    <t>0.2451,0.0573,0.7100,0.0394</t>
-  </si>
-  <si>
-    <t>0.0040,0.0043,0.9819,0.0373</t>
-  </si>
-  <si>
-    <t>0.0102,0.0382,0.9652,0.0215</t>
-  </si>
-  <si>
-    <t>0.0037,0.0065,0.9483,0.1170</t>
-  </si>
-  <si>
-    <t>0.0060,0.1177,0.9802,0.0036</t>
-  </si>
-  <si>
-    <t>0.0070,0.0130,0.9801,0.0182</t>
-  </si>
-  <si>
-    <t>0.9693,0.0206,0.0029,0.0079</t>
-  </si>
-  <si>
-    <t>0.9241,0.0815,0.0119,0.0097</t>
-  </si>
-  <si>
-    <t>0.9601,0.0266,0.0051,0.0092</t>
-  </si>
-  <si>
-    <t>0.9699,0.0196,0.0025,0.0080</t>
-  </si>
-  <si>
-    <t>0.9772,0.0176,0.0035,0.0034</t>
-  </si>
-  <si>
-    <t>0.9617,0.0291,0.0059,0.0064</t>
-  </si>
-  <si>
-    <t>0.9639,0.0240,0.0040,0.0077</t>
-  </si>
-  <si>
-    <t>0.9654,0.0285,0.0043,0.0061</t>
-  </si>
-  <si>
-    <t>0.0180,0.0047,0.9887,0.0017</t>
-  </si>
-  <si>
-    <t>0.3323,0.1670,0.5951,0.0193</t>
-  </si>
-  <si>
-    <t>0.5751,0.1375,0.2956,0.1251</t>
-  </si>
-  <si>
-    <t>0.0068,0.0024,0.9939,0.0040</t>
-  </si>
-  <si>
-    <t>0.0008,0.0021,0.9976,0.0029</t>
-  </si>
-  <si>
-    <t>0.0249,0.0595,0.9584,0.0041</t>
-  </si>
-  <si>
-    <t>0.0010,0.0040,0.9935,0.0101</t>
-  </si>
-  <si>
-    <t>0.0838,0.0688,0.8721,0.0270</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9989,0.0023</t>
-  </si>
-  <si>
-    <t>0.0023,0.0155,0.9706,0.0373</t>
-  </si>
-  <si>
-    <t>0.2674,0.0996,0.6800,0.0360</t>
-  </si>
-  <si>
-    <t>0.0896,0.0377,0.4998,0.5001</t>
-  </si>
-  <si>
-    <t>0.1761,0.0501,0.8141,0.0198</t>
-  </si>
-  <si>
-    <t>0.3754,0.1667,0.5394,0.0240</t>
-  </si>
-  <si>
-    <t>0.9765,0.0193,0.0016,0.0053</t>
-  </si>
-  <si>
-    <t>0.9399,0.0625,0.0135,0.0061</t>
-  </si>
-  <si>
-    <t>0.9743,0.0210,0.0038,0.0043</t>
-  </si>
-  <si>
-    <t>0.9551,0.0262,0.0114,0.0089</t>
-  </si>
-  <si>
-    <t>0.9589,0.0282,0.0034,0.0121</t>
-  </si>
-  <si>
-    <t>0.9763,0.0219,0.0031,0.0030</t>
-  </si>
-  <si>
-    <t>0.9666,0.0210,0.0037,0.0085</t>
-  </si>
-  <si>
-    <t>0.9650,0.0238,0.0033,0.0092</t>
-  </si>
-  <si>
-    <t>0.0377,0.1050,0.8662,0.0665</t>
-  </si>
-  <si>
-    <t>0.0030,0.0047,0.9947,0.0042</t>
-  </si>
-  <si>
-    <t>0.0045,0.0080,0.9890,0.0087</t>
-  </si>
-  <si>
-    <t>0.0285,0.0069,0.9441,0.0512</t>
-  </si>
-  <si>
-    <t>0.0031,0.0055,0.9939,0.0055</t>
-  </si>
-  <si>
-    <t>0.0654,0.0274,0.6683,0.3541</t>
-  </si>
-  <si>
-    <t>0.1121,0.0196,0.9168,0.0071</t>
-  </si>
-  <si>
-    <t>0.0292,0.0733,0.7802,0.2090</t>
-  </si>
-  <si>
-    <t>0.3492,0.0356,0.0145,0.6851</t>
-  </si>
-  <si>
-    <t>0.0151,0.0424,0.0146,0.9763</t>
-  </si>
-  <si>
-    <t>0.0502,0.0254,0.0083,0.9607</t>
-  </si>
-  <si>
-    <t>0.0038,0.0061,0.0010,0.9961</t>
-  </si>
-  <si>
-    <t>0.0074,0.0062,0.0016,0.9937</t>
-  </si>
-  <si>
-    <t>0.2134,0.1260,0.0491,0.7552</t>
+    <t>0.6310,0.0771,0.3446,0.0369</t>
+  </si>
+  <si>
+    <t>0.0077,0.0113,0.0029,0.9917</t>
+  </si>
+  <si>
+    <t>0.7772,0.0801,0.0454,0.1142</t>
+  </si>
+  <si>
+    <t>0.0347,0.0133,0.0092,0.9722</t>
+  </si>
+  <si>
+    <t>0.9819,0.0137,0.0016,0.0035</t>
+  </si>
+  <si>
+    <t>0.9727,0.0199,0.0033,0.0053</t>
+  </si>
+  <si>
+    <t>0.9687,0.0196,0.0046,0.0069</t>
+  </si>
+  <si>
+    <t>0.9737,0.0162,0.0044,0.0053</t>
+  </si>
+  <si>
+    <t>0.9644,0.0202,0.0034,0.0110</t>
+  </si>
+  <si>
+    <t>0.9733,0.0232,0.0035,0.0039</t>
+  </si>
+  <si>
+    <t>0.9729,0.0197,0.0020,0.0067</t>
+  </si>
+  <si>
+    <t>0.9824,0.0119,0.0015,0.0040</t>
+  </si>
+  <si>
+    <t>0.2542,0.1856,0.6459,0.0174</t>
+  </si>
+  <si>
+    <t>0.0555,0.0792,0.9206,0.0048</t>
+  </si>
+  <si>
+    <t>0.1287,0.0195,0.9162,0.0026</t>
+  </si>
+  <si>
+    <t>0.1168,0.0372,0.7974,0.0814</t>
+  </si>
+  <si>
+    <t>0.5273,0.0550,0.2565,0.1988</t>
+  </si>
+  <si>
+    <t>0.0494,0.9476,0.0255,0.0017</t>
+  </si>
+  <si>
+    <t>0.1491,0.7888,0.1448,0.0112</t>
+  </si>
+  <si>
+    <t>0.7921,0.2600,0.0271,0.0138</t>
+  </si>
+  <si>
+    <t>0.1895,0.8163,0.0539,0.0091</t>
+  </si>
+  <si>
+    <t>0.0786,0.9052,0.0694,0.0024</t>
+  </si>
+  <si>
+    <t>0.1849,0.0253,0.7399,0.0738</t>
+  </si>
+  <si>
+    <t>0.1055,0.0962,0.7313,0.1358</t>
+  </si>
+  <si>
+    <t>0.0019,0.0025,0.9957,0.0051</t>
+  </si>
+  <si>
+    <t>0.0592,0.0169,0.9404,0.0117</t>
+  </si>
+  <si>
+    <t>0.0941,0.0056,0.9050,0.0229</t>
+  </si>
+  <si>
+    <t>0.0246,0.0134,0.9472,0.0425</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9986,0.0028</t>
+  </si>
+  <si>
+    <t>0.2591,0.7230,0.0765,0.0207</t>
+  </si>
+  <si>
+    <t>0.3247,0.0383,0.7995,0.0033</t>
+  </si>
+  <si>
+    <t>0.0064,0.0151,0.9815,0.0157</t>
+  </si>
+  <si>
+    <t>0.1119,0.4830,0.5765,0.0344</t>
+  </si>
+  <si>
+    <t>0.7929,0.1653,0.0658,0.0406</t>
+  </si>
+  <si>
+    <t>0.3940,0.2967,0.3618,0.0268</t>
+  </si>
+  <si>
+    <t>0.8404,0.1558,0.0554,0.0115</t>
+  </si>
+  <si>
+    <t>0.1245,0.5064,0.4749,0.0109</t>
+  </si>
+  <si>
+    <t>0.0027,0.0240,0.9656,0.0368</t>
+  </si>
+  <si>
+    <t>0.0052,0.0147,0.9589,0.0560</t>
+  </si>
+  <si>
+    <t>0.0020,0.0190,0.9588,0.0616</t>
+  </si>
+  <si>
+    <t>0.0195,0.0101,0.7068,0.5027</t>
+  </si>
+  <si>
+    <t>0.0164,0.2305,0.9183,0.0184</t>
+  </si>
+  <si>
+    <t>0.0065,0.5656,0.9285,0.0021</t>
+  </si>
+  <si>
+    <t>0.0102,0.0246,0.9365,0.0701</t>
+  </si>
+  <si>
+    <t>0.3619,0.0958,0.1268,0.5447</t>
+  </si>
+  <si>
+    <t>0.0306,0.9426,0.0552,0.0051</t>
+  </si>
+  <si>
+    <t>0.0062,0.9317,0.4285,0.0021</t>
+  </si>
+  <si>
+    <t>0.0094,0.9670,0.1166,0.0025</t>
+  </si>
+  <si>
+    <t>0.0005,0.0081,0.9929,0.0108</t>
+  </si>
+  <si>
+    <t>0.0009,0.0031,0.9947,0.0098</t>
+  </si>
+  <si>
+    <t>0.0140,0.0045,0.9692,0.0286</t>
+  </si>
+  <si>
+    <t>0.0340,0.0062,0.9594,0.0202</t>
+  </si>
+  <si>
+    <t>0.0011,0.0018,0.9929,0.0172</t>
+  </si>
+  <si>
+    <t>0.0011,0.0015,0.9935,0.0175</t>
+  </si>
+  <si>
+    <t>0.9128,0.0741,0.0147,0.0148</t>
+  </si>
+  <si>
+    <t>0.9749,0.0182,0.0024,0.0053</t>
+  </si>
+  <si>
+    <t>0.9570,0.0271,0.0036,0.0123</t>
+  </si>
+  <si>
+    <t>0.0132,0.0110,0.9876,0.0039</t>
+  </si>
+  <si>
+    <t>0.9756,0.0156,0.0021,0.0065</t>
+  </si>
+  <si>
+    <t>0.9737,0.0198,0.0048,0.0037</t>
+  </si>
+  <si>
+    <t>0.9641,0.0278,0.0024,0.0090</t>
+  </si>
+  <si>
+    <t>0.0017,0.0229,0.9830,0.0154</t>
+  </si>
+  <si>
+    <t>0.0024,0.0212,0.9772,0.0217</t>
+  </si>
+  <si>
+    <t>0.0022,0.0059,0.9604,0.1045</t>
+  </si>
+  <si>
+    <t>0.0016,0.2091,0.9844,0.0027</t>
+  </si>
+  <si>
+    <t>0.0010,0.0022,0.9883,0.0341</t>
+  </si>
+  <si>
+    <t>0.0580,0.5502,0.6478,0.0047</t>
+  </si>
+  <si>
+    <t>0.0066,0.9493,0.2680,0.0012</t>
+  </si>
+  <si>
+    <t>0.2301,0.0997,0.7535,0.0072</t>
+  </si>
+  <si>
+    <t>0.7241,0.2115,0.1203,0.0389</t>
+  </si>
+  <si>
+    <t>0.0091,0.0267,0.9889,0.0019</t>
+  </si>
+  <si>
+    <t>0.0023,0.1841,0.9839,0.0021</t>
+  </si>
+  <si>
+    <t>0.0044,0.0819,0.9808,0.0073</t>
+  </si>
+  <si>
+    <t>0.0014,0.4029,0.9808,0.0016</t>
+  </si>
+  <si>
+    <t>0.0011,0.0870,0.9872,0.0037</t>
+  </si>
+  <si>
+    <t>0.0142,0.0117,0.0158,0.9819</t>
+  </si>
+  <si>
+    <t>0.0056,0.0101,0.0017,0.9940</t>
+  </si>
+  <si>
+    <t>0.0083,0.0056,0.0015,0.9934</t>
+  </si>
+  <si>
+    <t>0.0888,0.0195,0.0064,0.9420</t>
+  </si>
+  <si>
+    <t>0.0137,0.0127,0.0069,0.9860</t>
+  </si>
+  <si>
+    <t>0.0096,0.0122,0.0028,0.9901</t>
+  </si>
+  <si>
+    <t>0.0035,0.3387,0.9686,0.0033</t>
+  </si>
+  <si>
+    <t>0.0001,0.0157,0.9979,0.0013</t>
+  </si>
+  <si>
+    <t>0.0016,0.0359,0.9909,0.0043</t>
+  </si>
+  <si>
+    <t>0.0038,0.0304,0.9728,0.0251</t>
+  </si>
+  <si>
+    <t>0.0042,0.1510,0.9862,0.0020</t>
+  </si>
+  <si>
+    <t>0.0054,0.0641,0.9850,0.0043</t>
+  </si>
+  <si>
+    <t>0.9718,0.0219,0.0046,0.0044</t>
+  </si>
+  <si>
+    <t>0.9387,0.0633,0.0052,0.0085</t>
+  </si>
+  <si>
+    <t>0.9769,0.0207,0.0020,0.0041</t>
+  </si>
+  <si>
+    <t>0.9681,0.0277,0.0029,0.0062</t>
+  </si>
+  <si>
+    <t>0.9651,0.0317,0.0034,0.0063</t>
+  </si>
+  <si>
+    <t>0.9694,0.0184,0.0042,0.0076</t>
+  </si>
+  <si>
+    <t>0.9585,0.0325,0.0047,0.0089</t>
+  </si>
+  <si>
+    <t>0.9637,0.0333,0.0034,0.0069</t>
+  </si>
+  <si>
+    <t>0.9788,0.0136,0.0013,0.0061</t>
+  </si>
+  <si>
+    <t>0.9583,0.0241,0.0066,0.0102</t>
+  </si>
+  <si>
+    <t>0.9540,0.0333,0.0035,0.0133</t>
+  </si>
+  <si>
+    <t>0.9818,0.0136,0.0020,0.0033</t>
+  </si>
+  <si>
+    <t>0.9709,0.0195,0.0029,0.0069</t>
+  </si>
+  <si>
+    <t>0.9727,0.0190,0.0021,0.0069</t>
+  </si>
+  <si>
+    <t>0.9789,0.0169,0.0017,0.0041</t>
+  </si>
+  <si>
+    <t>0.9760,0.0123,0.0029,0.0061</t>
+  </si>
+  <si>
+    <t>0.0005,0.0007,0.9966,0.0092</t>
+  </si>
+  <si>
+    <t>0.0264,0.0044,0.9529,0.0323</t>
+  </si>
+  <si>
+    <t>0.3944,0.1268,0.4735,0.0997</t>
+  </si>
+  <si>
+    <t>0.0156,0.0199,0.9384,0.0598</t>
+  </si>
+  <si>
+    <t>0.2895,0.6892,0.1043,0.0096</t>
+  </si>
+  <si>
+    <t>0.1307,0.8305,0.0930,0.0070</t>
+  </si>
+  <si>
+    <t>0.2442,0.7871,0.0430,0.0074</t>
+  </si>
+  <si>
+    <t>0.4627,0.5560,0.0873,0.0136</t>
+  </si>
+  <si>
+    <t>0.1675,0.8475,0.0479,0.0036</t>
+  </si>
+  <si>
+    <t>0.1884,0.8076,0.0629,0.0088</t>
+  </si>
+  <si>
+    <t>0.6371,0.3644,0.0781,0.0075</t>
+  </si>
+  <si>
+    <t>0.3422,0.3822,0.3171,0.0157</t>
+  </si>
+  <si>
+    <t>0.1344,0.0279,0.8616,0.0183</t>
+  </si>
+  <si>
+    <t>0.2410,0.0993,0.3612,0.4093</t>
+  </si>
+  <si>
+    <t>0.2074,0.0498,0.8098,0.0079</t>
+  </si>
+  <si>
+    <t>0.4154,0.1650,0.2771,0.3102</t>
+  </si>
+  <si>
+    <t>0.0082,0.9725,0.1163,0.0009</t>
+  </si>
+  <si>
+    <t>0.0324,0.7939,0.5340,0.0117</t>
+  </si>
+  <si>
+    <t>0.1362,0.7287,0.2373,0.0190</t>
+  </si>
+  <si>
+    <t>0.0048,0.7320,0.9038,0.0025</t>
+  </si>
+  <si>
+    <t>0.0359,0.9373,0.0938,0.0026</t>
+  </si>
+  <si>
+    <t>0.8211,0.1531,0.0706,0.0137</t>
+  </si>
+  <si>
+    <t>0.7488,0.1845,0.1508,0.0116</t>
+  </si>
+  <si>
+    <t>0.8781,0.1206,0.0242,0.0139</t>
+  </si>
+  <si>
+    <t>0.8825,0.0357,0.0120,0.0714</t>
+  </si>
+  <si>
+    <t>0.9359,0.0479,0.0142,0.0109</t>
+  </si>
+  <si>
+    <t>0.9034,0.0563,0.0125,0.0322</t>
+  </si>
+  <si>
+    <t>0.9610,0.0229,0.0036,0.0121</t>
+  </si>
+  <si>
+    <t>0.7946,0.1390,0.0886,0.0294</t>
+  </si>
+  <si>
+    <t>0.9787,0.0161,0.0023,0.0041</t>
+  </si>
+  <si>
+    <t>0.9441,0.0302,0.0074,0.0182</t>
+  </si>
+  <si>
+    <t>0.0007,0.0103,0.9974,0.0013</t>
+  </si>
+  <si>
+    <t>0.0028,0.0248,0.9905,0.0056</t>
+  </si>
+  <si>
+    <t>0.0045,0.0145,0.9860,0.0118</t>
+  </si>
+  <si>
+    <t>0.0070,0.0895,0.9850,0.0013</t>
+  </si>
+  <si>
+    <t>0.1541,0.0721,0.1953,0.7345</t>
+  </si>
+  <si>
+    <t>0.5788,0.0924,0.3506,0.0759</t>
+  </si>
+  <si>
+    <t>0.1410,0.0183,0.8007,0.0636</t>
+  </si>
+  <si>
+    <t>0.2431,0.3117,0.5209,0.0184</t>
+  </si>
+  <si>
+    <t>0.0179,0.0091,0.0023,0.9871</t>
+  </si>
+  <si>
+    <t>0.0006,0.0025,0.0009,0.9989</t>
+  </si>
+  <si>
+    <t>0.0012,0.0061,0.0011,0.9979</t>
+  </si>
+  <si>
+    <t>0.0189,0.0157,0.0131,0.9791</t>
+  </si>
+  <si>
+    <t>0.0041,0.3593,0.9519,0.0056</t>
+  </si>
+  <si>
+    <t>0.9645,0.0275,0.0035,0.0071</t>
+  </si>
+  <si>
+    <t>0.6702,0.3648,0.0484,0.0317</t>
+  </si>
+  <si>
+    <t>0.9392,0.0212,0.0029,0.0316</t>
+  </si>
+  <si>
+    <t>0.9316,0.0563,0.0229,0.0082</t>
+  </si>
+  <si>
+    <t>0.9044,0.0781,0.0298,0.0121</t>
+  </si>
+  <si>
+    <t>0.4730,0.0521,0.1060,0.4060</t>
+  </si>
+  <si>
+    <t>0.9084,0.0417,0.0068,0.0421</t>
+  </si>
+  <si>
+    <t>0.0112,0.0157,0.9118,0.1134</t>
+  </si>
+  <si>
+    <t>0.8181,0.0810,0.0436,0.0609</t>
+  </si>
+  <si>
+    <t>0.8640,0.0450,0.0143,0.0609</t>
+  </si>
+  <si>
+    <t>0.3759,0.5410,0.1775,0.0385</t>
+  </si>
+  <si>
+    <t>0.8024,0.1562,0.0680,0.0240</t>
+  </si>
+  <si>
+    <t>0.7408,0.1202,0.2062,0.0147</t>
+  </si>
+  <si>
+    <t>0.3527,0.7016,0.0477,0.0109</t>
+  </si>
+  <si>
+    <t>0.5274,0.3826,0.1663,0.0480</t>
+  </si>
+  <si>
+    <t>0.6219,0.2204,0.1609,0.1279</t>
+  </si>
+  <si>
+    <t>0.9511,0.0202,0.0050,0.0204</t>
+  </si>
+  <si>
+    <t>0.9683,0.0192,0.0027,0.0090</t>
+  </si>
+  <si>
+    <t>0.9705,0.0175,0.0039,0.0064</t>
+  </si>
+  <si>
+    <t>0.9643,0.0232,0.0049,0.0080</t>
+  </si>
+  <si>
+    <t>0.9667,0.0234,0.0026,0.0086</t>
+  </si>
+  <si>
+    <t>0.9700,0.0176,0.0039,0.0078</t>
+  </si>
+  <si>
+    <t>0.9614,0.0174,0.0037,0.0145</t>
+  </si>
+  <si>
+    <t>0.9653,0.0173,0.0022,0.0131</t>
+  </si>
+  <si>
+    <t>0.6098,0.4698,0.0369,0.0241</t>
+  </si>
+  <si>
+    <t>0.4932,0.5597,0.0494,0.0115</t>
+  </si>
+  <si>
+    <t>0.7935,0.2650,0.0302,0.0098</t>
+  </si>
+  <si>
+    <t>0.7938,0.1019,0.1574,0.0187</t>
+  </si>
+  <si>
+    <t>0.9466,0.0749,0.0051,0.0038</t>
+  </si>
+  <si>
+    <t>0.8267,0.1176,0.0735,0.0250</t>
+  </si>
+  <si>
+    <t>0.9176,0.0487,0.0088,0.0273</t>
+  </si>
+  <si>
+    <t>0.8340,0.1731,0.0443,0.0154</t>
+  </si>
+  <si>
+    <t>0.0050,0.0080,0.9941,0.0019</t>
+  </si>
+  <si>
+    <t>0.9436,0.0255,0.0046,0.0232</t>
+  </si>
+  <si>
+    <t>0.0169,0.0126,0.9804,0.0053</t>
+  </si>
+  <si>
+    <t>0.0011,0.0056,0.9892,0.0170</t>
+  </si>
+  <si>
+    <t>0.1733,0.0261,0.8685,0.0086</t>
+  </si>
+  <si>
+    <t>0.0136,0.0454,0.9694,0.0098</t>
+  </si>
+  <si>
+    <t>0.0026,0.0040,0.9965,0.0020</t>
+  </si>
+  <si>
+    <t>0.0081,0.0293,0.9860,0.0034</t>
+  </si>
+  <si>
+    <t>0.0018,0.0016,0.9981,0.0012</t>
+  </si>
+  <si>
+    <t>0.2337,0.0473,0.8068,0.0078</t>
+  </si>
+  <si>
+    <t>0.1534,0.0133,0.9161,0.0025</t>
+  </si>
+  <si>
+    <t>0.3419,0.1161,0.6295,0.0151</t>
+  </si>
+  <si>
+    <t>0.1051,0.1875,0.8172,0.0060</t>
+  </si>
+  <si>
+    <t>0.1382,0.3653,0.6094,0.0153</t>
+  </si>
+  <si>
+    <t>0.0886,0.1073,0.8659,0.0130</t>
+  </si>
+  <si>
+    <t>0.3933,0.1782,0.5072,0.0214</t>
+  </si>
+  <si>
+    <t>0.2832,0.2384,0.5587,0.0307</t>
+  </si>
+  <si>
+    <t>0.9021,0.1009,0.0236,0.0077</t>
+  </si>
+  <si>
+    <t>0.7493,0.2884,0.0406,0.0144</t>
+  </si>
+  <si>
+    <t>0.9334,0.0614,0.0148,0.0077</t>
+  </si>
+  <si>
+    <t>0.9716,0.0237,0.0032,0.0050</t>
+  </si>
+  <si>
+    <t>0.9448,0.0621,0.0063,0.0062</t>
+  </si>
+  <si>
+    <t>0.3535,0.1173,0.5964,0.0339</t>
+  </si>
+  <si>
+    <t>0.3679,0.0694,0.6722,0.0148</t>
+  </si>
+  <si>
+    <t>0.2702,0.0727,0.2357,0.5156</t>
+  </si>
+  <si>
+    <t>0.1878,0.2002,0.6849,0.0221</t>
+  </si>
+  <si>
+    <t>0.4096,0.1279,0.5294,0.0535</t>
+  </si>
+  <si>
+    <t>0.0033,0.0062,0.9461,0.1434</t>
+  </si>
+  <si>
+    <t>0.0039,0.0350,0.9534,0.0466</t>
+  </si>
+  <si>
+    <t>0.0051,0.0480,0.9648,0.0257</t>
+  </si>
+  <si>
+    <t>0.0024,0.0164,0.9761,0.0280</t>
+  </si>
+  <si>
+    <t>0.0024,0.0052,0.9943,0.0059</t>
+  </si>
+  <si>
+    <t>0.9548,0.0335,0.0067,0.0087</t>
+  </si>
+  <si>
+    <t>0.9724,0.0151,0.0024,0.0092</t>
+  </si>
+  <si>
+    <t>0.9647,0.0294,0.0047,0.0074</t>
+  </si>
+  <si>
+    <t>0.9800,0.0136,0.0024,0.0044</t>
+  </si>
+  <si>
+    <t>0.9764,0.0204,0.0022,0.0039</t>
+  </si>
+  <si>
+    <t>0.9703,0.0222,0.0044,0.0054</t>
+  </si>
+  <si>
+    <t>0.9757,0.0144,0.0017,0.0069</t>
+  </si>
+  <si>
+    <t>0.9644,0.0197,0.0046,0.0092</t>
+  </si>
+  <si>
+    <t>0.4139,0.0490,0.7042,0.0070</t>
+  </si>
+  <si>
+    <t>0.4944,0.1323,0.5016,0.0148</t>
+  </si>
+  <si>
+    <t>0.6138,0.0523,0.3662,0.0650</t>
+  </si>
+  <si>
+    <t>0.0005,0.0009,0.9986,0.0028</t>
+  </si>
+  <si>
+    <t>0.0024,0.0026,0.9958,0.0040</t>
+  </si>
+  <si>
+    <t>0.0062,0.0073,0.9924,0.0033</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.9852,0.0796</t>
+  </si>
+  <si>
+    <t>0.1368,0.0944,0.8182,0.0151</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9996,0.0013</t>
+  </si>
+  <si>
+    <t>0.0038,0.0180,0.9872,0.0087</t>
+  </si>
+  <si>
+    <t>0.3561,0.2201,0.5084,0.0875</t>
+  </si>
+  <si>
+    <t>0.0631,0.0529,0.2736,0.7736</t>
+  </si>
+  <si>
+    <t>0.2414,0.0624,0.7933,0.0125</t>
+  </si>
+  <si>
+    <t>0.3477,0.0422,0.6858,0.0335</t>
+  </si>
+  <si>
+    <t>0.9679,0.0213,0.0031,0.0078</t>
+  </si>
+  <si>
+    <t>0.9659,0.0233,0.0031,0.0087</t>
+  </si>
+  <si>
+    <t>0.9771,0.0159,0.0023,0.0048</t>
+  </si>
+  <si>
+    <t>0.9621,0.0320,0.0062,0.0063</t>
+  </si>
+  <si>
+    <t>0.9702,0.0201,0.0031,0.0071</t>
+  </si>
+  <si>
+    <t>0.9765,0.0175,0.0023,0.0046</t>
+  </si>
+  <si>
+    <t>0.9653,0.0270,0.0045,0.0063</t>
+  </si>
+  <si>
+    <t>0.9621,0.0244,0.0034,0.0106</t>
+  </si>
+  <si>
+    <t>0.0296,0.0805,0.9438,0.0091</t>
+  </si>
+  <si>
+    <t>0.0032,0.0049,0.9968,0.0010</t>
+  </si>
+  <si>
+    <t>0.0012,0.0008,0.9969,0.0064</t>
+  </si>
+  <si>
+    <t>0.0776,0.0684,0.8641,0.0360</t>
+  </si>
+  <si>
+    <t>0.0018,0.0020,0.9952,0.0070</t>
+  </si>
+  <si>
+    <t>0.0453,0.0141,0.8716,0.1091</t>
+  </si>
+  <si>
+    <t>0.0783,0.0271,0.8474,0.0807</t>
+  </si>
+  <si>
+    <t>0.0065,0.0197,0.5899,0.6074</t>
+  </si>
+  <si>
+    <t>0.5645,0.0524,0.1402,0.2970</t>
+  </si>
+  <si>
+    <t>0.0132,0.0126,0.0028,0.9880</t>
+  </si>
+  <si>
+    <t>0.0173,0.0110,0.0031,0.9863</t>
+  </si>
+  <si>
+    <t>0.0033,0.0057,0.0014,0.9962</t>
+  </si>
+  <si>
+    <t>0.0032,0.0047,0.0009,0.9968</t>
+  </si>
+  <si>
+    <t>0.2124,0.0849,0.0588,0.7844</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2228,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2452,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,10 +2463,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2480,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2519,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,10 +2547,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,10 +2561,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,10 +2603,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2858,7 @@
         <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,10 +2883,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2928,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,10 +2953,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2970,7 @@
         <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>261</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2995,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3096,7 @@
         <v>261</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3110,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3124,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3138,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>261</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3166,7 @@
         <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3429,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3499,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3544,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3600,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,10 +3639,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,10 +3653,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3838,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3852,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,10 +3891,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4006,7 @@
         <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4034,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,10 +4115,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4199,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4353,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4367,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4398,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4636,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4692,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4790,7 @@
         <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4801,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4818,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4832,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5182,7 @@
         <v>260</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5196,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>261</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,10 +5431,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5445,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5518,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
